--- a/results/DUNE_HV_Crate_Production_Test.xlsx
+++ b/results/DUNE_HV_Crate_Production_Test.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:IA77"/>
+  <dimension ref="A1:IA79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="25.37" customWidth="1" style="5" min="1" max="1"/>
@@ -24130,14 +24130,48 @@
           <t>lke</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>09/10/2026</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>02:07:13 PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>lke</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>09/11/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>11:45:26 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>lke</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>09/11/2026</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>11:51:04 AM</t>
         </is>
       </c>
     </row>
